--- a/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="173">
   <si>
     <t>校区</t>
   </si>
@@ -432,6 +432,120 @@
   </si>
   <si>
     <t>Q230103(TG)</t>
+  </si>
+  <si>
+    <t>外国语学院</t>
+  </si>
+  <si>
+    <t>WY127200S</t>
+  </si>
+  <si>
+    <t>日本古典语法</t>
+  </si>
+  <si>
+    <t>B231607</t>
+  </si>
+  <si>
+    <t>洪洁</t>
+  </si>
+  <si>
+    <t>第9周周1(2026-04-27) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>B231608</t>
+  </si>
+  <si>
+    <t>数字媒体与设计艺术学院</t>
+  </si>
+  <si>
+    <t>CM1105D2S</t>
+  </si>
+  <si>
+    <t>马克思主义新闻思想</t>
+  </si>
+  <si>
+    <t>B221202</t>
+  </si>
+  <si>
+    <t>程河清</t>
+  </si>
+  <si>
+    <t>第12周周5(2026-05-22) 10:25-12:15</t>
+  </si>
+  <si>
+    <t>教1－401</t>
+  </si>
+  <si>
+    <t>B231201</t>
+  </si>
+  <si>
+    <t>B231202</t>
+  </si>
+  <si>
+    <t>B240703</t>
+  </si>
+  <si>
+    <t>B241101</t>
+  </si>
+  <si>
+    <t>B251203</t>
+  </si>
+  <si>
+    <t>CM120800S</t>
+  </si>
+  <si>
+    <t>艺术设计理论</t>
+  </si>
+  <si>
+    <t>B231203</t>
+  </si>
+  <si>
+    <t>徐子涵</t>
+  </si>
+  <si>
+    <t>第13周周2(2026-05-26) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>教4－308</t>
+  </si>
+  <si>
+    <t>B231204</t>
+  </si>
+  <si>
+    <t>教4－309</t>
+  </si>
+  <si>
+    <t>B241106</t>
+  </si>
+  <si>
+    <t>B241107</t>
+  </si>
+  <si>
+    <t>WY111500S</t>
+  </si>
+  <si>
+    <t>学术论文写作与研究方法</t>
+  </si>
+  <si>
+    <t>B231601</t>
+  </si>
+  <si>
+    <t>包莉</t>
+  </si>
+  <si>
+    <t>教2－303</t>
+  </si>
+  <si>
+    <t>B231602</t>
+  </si>
+  <si>
+    <t>B231603</t>
+  </si>
+  <si>
+    <t>教2－304</t>
+  </si>
+  <si>
+    <t>B231604</t>
   </si>
 </sst>
 </file>
@@ -799,7 +913,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -834,6 +948,21 @@
       </top>
       <bottom style="thin">
         <color indexed="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="0"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -961,7 +1090,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -973,34 +1102,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1085,7 +1214,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1108,6 +1237,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1635,18 +1770,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="20.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.25" style="2" customWidth="1"/>
     <col min="3" max="3" width="14.125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="7.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="34.125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
@@ -3911,6 +4046,470 @@
         <v>31</v>
       </c>
     </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="G79" s="8">
+        <v>19</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G80" s="6">
+        <v>18</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G81" s="9">
+        <v>1</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G82" s="9">
+        <v>2</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G83" s="9">
+        <v>3</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G84" s="9">
+        <v>1</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G85" s="9">
+        <v>5</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="E86" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G86" s="9">
+        <v>25</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G87" s="9">
+        <v>36</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G88" s="9">
+        <v>34</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G89" s="9">
+        <v>20</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G90" s="9">
+        <v>20</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G91" s="6">
+        <v>25</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G92" s="6">
+        <v>30</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G93" s="6">
+        <v>26</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="G94" s="6">
+        <v>24</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期考试安排表（学院组织）-学生用表.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$228</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="322">
   <si>
     <t>校区</t>
   </si>
@@ -374,192 +377,192 @@
     <t>第12周周6(2026-05-23) 13:30-15:20</t>
   </si>
   <si>
+    <t>教4－308</t>
+  </si>
+  <si>
+    <t>B220511</t>
+  </si>
+  <si>
+    <t>B220512</t>
+  </si>
+  <si>
+    <t>B230511</t>
+  </si>
+  <si>
+    <t>B230512</t>
+  </si>
+  <si>
+    <t>ZD1433F3C</t>
+  </si>
+  <si>
+    <t>徐霄</t>
+  </si>
+  <si>
+    <t>教2－212</t>
+  </si>
+  <si>
+    <t>ZD160600S</t>
+  </si>
+  <si>
+    <t>深度学习（双语）</t>
+  </si>
+  <si>
+    <t>B230515</t>
+  </si>
+  <si>
+    <t>宋杰</t>
+  </si>
+  <si>
+    <t>B230516</t>
+  </si>
+  <si>
+    <t>B230517</t>
+  </si>
+  <si>
+    <t>Q230101(RZ)</t>
+  </si>
+  <si>
+    <t>ZD161000C</t>
+  </si>
+  <si>
+    <t>机器人学基础</t>
+  </si>
+  <si>
+    <t>王彩玲</t>
+  </si>
+  <si>
+    <t>第13周周3(2026-05-27) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>Q230103(TG)</t>
+  </si>
+  <si>
+    <t>外国语学院</t>
+  </si>
+  <si>
+    <t>WY127200S</t>
+  </si>
+  <si>
+    <t>日本古典语法</t>
+  </si>
+  <si>
+    <t>B231607</t>
+  </si>
+  <si>
+    <t>洪洁</t>
+  </si>
+  <si>
+    <t>第9周周1(2026-04-27) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>B231608</t>
+  </si>
+  <si>
+    <t>数字媒体与设计艺术学院</t>
+  </si>
+  <si>
+    <t>CM1105D2S</t>
+  </si>
+  <si>
+    <t>马克思主义新闻思想</t>
+  </si>
+  <si>
+    <t>B221202</t>
+  </si>
+  <si>
+    <t>程河清</t>
+  </si>
+  <si>
+    <t>第12周周5(2026-05-22) 10:25-12:15</t>
+  </si>
+  <si>
+    <t>教1－401</t>
+  </si>
+  <si>
+    <t>B231201</t>
+  </si>
+  <si>
+    <t>B231202</t>
+  </si>
+  <si>
+    <t>B240703</t>
+  </si>
+  <si>
+    <t>B241101</t>
+  </si>
+  <si>
+    <t>B251203</t>
+  </si>
+  <si>
+    <t>CM120800S</t>
+  </si>
+  <si>
+    <t>艺术设计理论</t>
+  </si>
+  <si>
+    <t>B231203</t>
+  </si>
+  <si>
+    <t>徐子涵</t>
+  </si>
+  <si>
+    <t>第13周周2(2026-05-26) 16:00-17:50</t>
+  </si>
+  <si>
+    <t>B231204</t>
+  </si>
+  <si>
+    <t>教4－309</t>
+  </si>
+  <si>
+    <t>B241106</t>
+  </si>
+  <si>
+    <t>B241107</t>
+  </si>
+  <si>
+    <t>WY111500S</t>
+  </si>
+  <si>
+    <t>学术论文写作与研究方法</t>
+  </si>
+  <si>
+    <t>B231601</t>
+  </si>
+  <si>
+    <t>包莉</t>
+  </si>
+  <si>
+    <t>教2－303</t>
+  </si>
+  <si>
+    <t>B231602</t>
+  </si>
+  <si>
+    <t>B231603</t>
+  </si>
+  <si>
+    <t>教2－304</t>
+  </si>
+  <si>
+    <t>B231604</t>
+  </si>
+  <si>
+    <t>通信与信息工程学院</t>
+  </si>
+  <si>
+    <t>TXXD09T0C</t>
+  </si>
+  <si>
+    <t>股票交易技术</t>
+  </si>
+  <si>
+    <t>朱成</t>
+  </si>
+  <si>
     <t>教2－208</t>
   </si>
   <si>
-    <t>B220511</t>
-  </si>
-  <si>
-    <t>B220512</t>
-  </si>
-  <si>
-    <t>B230511</t>
-  </si>
-  <si>
-    <t>B230512</t>
-  </si>
-  <si>
-    <t>ZD1433F3C</t>
-  </si>
-  <si>
-    <t>徐霄</t>
-  </si>
-  <si>
-    <t>教2－212</t>
-  </si>
-  <si>
-    <t>ZD160600S</t>
-  </si>
-  <si>
-    <t>深度学习（双语）</t>
-  </si>
-  <si>
-    <t>B230515</t>
-  </si>
-  <si>
-    <t>宋杰</t>
-  </si>
-  <si>
-    <t>B230516</t>
-  </si>
-  <si>
-    <t>B230517</t>
-  </si>
-  <si>
-    <t>Q230101(RZ)</t>
-  </si>
-  <si>
-    <t>ZD161000C</t>
-  </si>
-  <si>
-    <t>机器人学基础</t>
-  </si>
-  <si>
-    <t>王彩玲</t>
-  </si>
-  <si>
-    <t>第13周周3(2026-05-27) 13:30-15:20</t>
-  </si>
-  <si>
-    <t>Q230103(TG)</t>
-  </si>
-  <si>
-    <t>外国语学院</t>
-  </si>
-  <si>
-    <t>WY127200S</t>
-  </si>
-  <si>
-    <t>日本古典语法</t>
-  </si>
-  <si>
-    <t>B231607</t>
-  </si>
-  <si>
-    <t>洪洁</t>
-  </si>
-  <si>
-    <t>第9周周1(2026-04-27) 13:30-15:20</t>
-  </si>
-  <si>
-    <t>B231608</t>
-  </si>
-  <si>
-    <t>数字媒体与设计艺术学院</t>
-  </si>
-  <si>
-    <t>CM1105D2S</t>
-  </si>
-  <si>
-    <t>马克思主义新闻思想</t>
-  </si>
-  <si>
-    <t>B221202</t>
-  </si>
-  <si>
-    <t>程河清</t>
-  </si>
-  <si>
-    <t>第12周周5(2026-05-22) 10:25-12:15</t>
-  </si>
-  <si>
-    <t>教1－401</t>
-  </si>
-  <si>
-    <t>B231201</t>
-  </si>
-  <si>
-    <t>B231202</t>
-  </si>
-  <si>
-    <t>B240703</t>
-  </si>
-  <si>
-    <t>B241101</t>
-  </si>
-  <si>
-    <t>B251203</t>
-  </si>
-  <si>
-    <t>CM120800S</t>
-  </si>
-  <si>
-    <t>艺术设计理论</t>
-  </si>
-  <si>
-    <t>B231203</t>
-  </si>
-  <si>
-    <t>徐子涵</t>
-  </si>
-  <si>
-    <t>第13周周2(2026-05-26) 16:00-17:50</t>
-  </si>
-  <si>
-    <t>教4－308</t>
-  </si>
-  <si>
-    <t>B231204</t>
-  </si>
-  <si>
-    <t>教4－309</t>
-  </si>
-  <si>
-    <t>B241106</t>
-  </si>
-  <si>
-    <t>B241107</t>
-  </si>
-  <si>
-    <t>WY111500S</t>
-  </si>
-  <si>
-    <t>学术论文写作与研究方法</t>
-  </si>
-  <si>
-    <t>B231601</t>
-  </si>
-  <si>
-    <t>包莉</t>
-  </si>
-  <si>
-    <t>教2－303</t>
-  </si>
-  <si>
-    <t>B231602</t>
-  </si>
-  <si>
-    <t>B231603</t>
-  </si>
-  <si>
-    <t>教2－304</t>
-  </si>
-  <si>
-    <t>B231604</t>
-  </si>
-  <si>
-    <t>通信与信息工程学院</t>
-  </si>
-  <si>
-    <t>TXXD09T0C</t>
-  </si>
-  <si>
-    <t>股票交易技术</t>
-  </si>
-  <si>
-    <t>朱成</t>
-  </si>
-  <si>
     <t>B240303</t>
   </si>
   <si>
@@ -891,6 +894,108 @@
   </si>
   <si>
     <t>杨朝雁</t>
+  </si>
+  <si>
+    <t>DG1324F4S</t>
+  </si>
+  <si>
+    <t>光纤通信系统（混合式）</t>
+  </si>
+  <si>
+    <t>B230214</t>
+  </si>
+  <si>
+    <t>汪静丽</t>
+  </si>
+  <si>
+    <t>B230221</t>
+  </si>
+  <si>
+    <t>B230215</t>
+  </si>
+  <si>
+    <t>B220216</t>
+  </si>
+  <si>
+    <t>B230213</t>
+  </si>
+  <si>
+    <t>廖晨</t>
+  </si>
+  <si>
+    <t>B220220</t>
+  </si>
+  <si>
+    <t>B220217</t>
+  </si>
+  <si>
+    <t>B230216</t>
+  </si>
+  <si>
+    <t>B230217</t>
+  </si>
+  <si>
+    <t>B230218</t>
+  </si>
+  <si>
+    <t>杜建新</t>
+  </si>
+  <si>
+    <t>B230219</t>
+  </si>
+  <si>
+    <t>B230220</t>
+  </si>
+  <si>
+    <t>ZD1203F4S</t>
+  </si>
+  <si>
+    <t>自动控制理论(混合式)</t>
+  </si>
+  <si>
+    <t>杨敏</t>
+  </si>
+  <si>
+    <t>第15周周3(2026-06-10) 13:30-15:20</t>
+  </si>
+  <si>
+    <t>教2－203</t>
+  </si>
+  <si>
+    <t>ZD1203F1S</t>
+  </si>
+  <si>
+    <t>自动控制原理（混合式）</t>
+  </si>
+  <si>
+    <t>B220514</t>
+  </si>
+  <si>
+    <t>B220515</t>
+  </si>
+  <si>
+    <t>B230513</t>
+  </si>
+  <si>
+    <t>B230514</t>
+  </si>
+  <si>
+    <t>ZD1203F5S</t>
+  </si>
+  <si>
+    <t>自动控制原理</t>
+  </si>
+  <si>
+    <t>B230500</t>
+  </si>
+  <si>
+    <t>B230501</t>
+  </si>
+  <si>
+    <t>B230502</t>
+  </si>
+  <si>
+    <t>B230503</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I213"/>
+  <dimension ref="A1:I242"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -4613,7 +4718,7 @@
         <v>158</v>
       </c>
       <c r="I87" s="6" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -4630,7 +4735,7 @@
         <v>155</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>157</v>
@@ -4642,7 +4747,7 @@
         <v>158</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -4659,7 +4764,7 @@
         <v>155</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>157</v>
@@ -4671,7 +4776,7 @@
         <v>158</v>
       </c>
       <c r="I89" s="6" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -4688,7 +4793,7 @@
         <v>155</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>157</v>
@@ -4700,7 +4805,7 @@
         <v>158</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -4711,16 +4816,16 @@
         <v>135</v>
       </c>
       <c r="C91" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D91" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="E91" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="E91" s="6" t="s">
+      <c r="F91" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="G91" s="6">
         <v>25</v>
@@ -4729,7 +4834,7 @@
         <v>15</v>
       </c>
       <c r="I91" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -4740,16 +4845,16 @@
         <v>135</v>
       </c>
       <c r="C92" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="E92" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G92" s="6">
         <v>30</v>
@@ -4758,7 +4863,7 @@
         <v>15</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -4769,16 +4874,16 @@
         <v>135</v>
       </c>
       <c r="C93" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D93" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D93" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="E93" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G93" s="6">
         <v>26</v>
@@ -4787,7 +4892,7 @@
         <v>15</v>
       </c>
       <c r="I93" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -4798,16 +4903,16 @@
         <v>135</v>
       </c>
       <c r="C94" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D94" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="D94" s="6" t="s">
-        <v>165</v>
-      </c>
       <c r="E94" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G94" s="6">
         <v>24</v>
@@ -4816,1688 +4921,1688 @@
         <v>15</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="D95" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="E95" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F95" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E95" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F95" s="7" t="s">
+      <c r="G95" s="6">
+        <v>1</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I95" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G95" s="7">
-        <v>1</v>
-      </c>
-      <c r="H95" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I95" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="D96" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="E96" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F96" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E96" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F96" s="7" t="s">
+      <c r="G96" s="6">
+        <v>2</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I96" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G96" s="7">
-        <v>2</v>
-      </c>
-      <c r="H96" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I96" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="D97" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="E97" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F97" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E97" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F97" s="7" t="s">
+      <c r="G97" s="6">
+        <v>1</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I97" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G97" s="7">
-        <v>1</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I97" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="D98" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="E98" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F98" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E98" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F98" s="7" t="s">
+      <c r="G98" s="6">
+        <v>1</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I98" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G98" s="7">
-        <v>1</v>
-      </c>
-      <c r="H98" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I98" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C99" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="D99" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="E99" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F99" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E99" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F99" s="7" t="s">
+      <c r="G99" s="6">
+        <v>1</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I99" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G99" s="7">
-        <v>1</v>
-      </c>
-      <c r="H99" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I99" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="D100" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="E100" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F100" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F100" s="7" t="s">
+      <c r="G100" s="6">
+        <v>2</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I100" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G100" s="7">
-        <v>2</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I100" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C101" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="D101" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="E101" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F101" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E101" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F101" s="7" t="s">
+      <c r="G101" s="6">
+        <v>1</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I101" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G101" s="7">
-        <v>1</v>
-      </c>
-      <c r="H101" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I101" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="D102" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="E102" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F102" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F102" s="7" t="s">
+      <c r="G102" s="6">
+        <v>1</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I102" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G102" s="7">
-        <v>1</v>
-      </c>
-      <c r="H102" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I102" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C103" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="D103" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="E103" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F103" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F103" s="7" t="s">
+      <c r="G103" s="6">
+        <v>1</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I103" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G103" s="7">
-        <v>1</v>
-      </c>
-      <c r="H103" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I103" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="D104" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="E104" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F104" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F104" s="7" t="s">
+      <c r="G104" s="6">
+        <v>1</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I104" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G104" s="7">
-        <v>1</v>
-      </c>
-      <c r="H104" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I104" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C105" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="D105" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="E105" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F105" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E105" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="F105" s="7" t="s">
+      <c r="G105" s="6">
+        <v>5</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I105" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G105" s="7">
-        <v>5</v>
-      </c>
-      <c r="H105" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="D106" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="E106" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F106" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E106" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="F106" s="7" t="s">
+      <c r="G106" s="6">
+        <v>1</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I106" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G106" s="7">
-        <v>1</v>
-      </c>
-      <c r="H106" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I106" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C107" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="D107" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="E107" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F107" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E107" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="F107" s="7" t="s">
+      <c r="G107" s="6">
+        <v>1</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I107" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G107" s="7">
-        <v>1</v>
-      </c>
-      <c r="H107" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I107" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C108" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="D108" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="E108" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F108" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F108" s="7" t="s">
+      <c r="G108" s="6">
+        <v>1</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I108" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G108" s="7">
-        <v>1</v>
-      </c>
-      <c r="H108" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I108" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="D109" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="E109" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F109" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E109" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F109" s="7" t="s">
+      <c r="G109" s="6">
+        <v>2</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I109" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G109" s="7">
-        <v>2</v>
-      </c>
-      <c r="H109" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I109" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="D110" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="E110" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F110" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E110" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F110" s="7" t="s">
+      <c r="G110" s="6">
+        <v>3</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I110" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G110" s="7">
-        <v>3</v>
-      </c>
-      <c r="H110" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I110" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C111" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="D111" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="E111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E111" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F111" s="7" t="s">
+      <c r="G111" s="6">
+        <v>1</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I111" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G111" s="7">
-        <v>1</v>
-      </c>
-      <c r="H111" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I111" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C112" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="D112" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="E112" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F112" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E112" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="F112" s="7" t="s">
+      <c r="G112" s="6">
+        <v>1</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I112" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G112" s="7">
-        <v>1</v>
-      </c>
-      <c r="H112" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I112" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C113" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="D113" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D113" s="7" t="s">
+      <c r="E113" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F113" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E113" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="F113" s="7" t="s">
+      <c r="G113" s="6">
+        <v>1</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I113" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G113" s="7">
-        <v>1</v>
-      </c>
-      <c r="H113" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I113" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="D114" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="E114" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F114" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E114" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="F114" s="7" t="s">
+      <c r="G114" s="6">
+        <v>1</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I114" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G114" s="7">
-        <v>1</v>
-      </c>
-      <c r="H114" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I114" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="D115" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D115" s="7" t="s">
+      <c r="E115" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F115" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E115" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="F115" s="7" t="s">
+      <c r="G115" s="6">
+        <v>1</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I115" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G115" s="7">
-        <v>1</v>
-      </c>
-      <c r="H115" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I115" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="D116" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="E116" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F116" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E116" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="F116" s="7" t="s">
+      <c r="G116" s="6">
+        <v>1</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I116" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G116" s="7">
-        <v>1</v>
-      </c>
-      <c r="H116" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I116" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C117" s="7" t="s">
+      <c r="D117" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D117" s="7" t="s">
+      <c r="E117" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F117" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E117" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="F117" s="7" t="s">
+      <c r="G117" s="6">
+        <v>1</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I117" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G117" s="7">
-        <v>1</v>
-      </c>
-      <c r="H117" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I117" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C118" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C118" s="7" t="s">
+      <c r="D118" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="E118" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F118" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E118" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="F118" s="7" t="s">
+      <c r="G118" s="6">
+        <v>2</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I118" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G118" s="7">
-        <v>2</v>
-      </c>
-      <c r="H118" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I118" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C119" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="D119" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D119" s="7" t="s">
+      <c r="E119" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F119" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E119" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F119" s="7" t="s">
+      <c r="G119" s="6">
+        <v>1</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I119" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G119" s="7">
-        <v>1</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="B120" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C120" s="7" t="s">
+      <c r="D120" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D120" s="7" t="s">
+      <c r="E120" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F120" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E120" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F120" s="7" t="s">
+      <c r="G120" s="6">
+        <v>1</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I120" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G120" s="7">
-        <v>1</v>
-      </c>
-      <c r="H120" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I120" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C121" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C121" s="7" t="s">
+      <c r="D121" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D121" s="7" t="s">
+      <c r="E121" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F121" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E121" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="F121" s="7" t="s">
+      <c r="G121" s="6">
+        <v>1</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I121" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G121" s="7">
-        <v>1</v>
-      </c>
-      <c r="H121" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I121" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C122" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="D122" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="E122" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F122" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E122" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="F122" s="7" t="s">
+      <c r="G122" s="6">
+        <v>1</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I122" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G122" s="7">
-        <v>1</v>
-      </c>
-      <c r="H122" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I122" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="B123" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C123" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C123" s="7" t="s">
+      <c r="D123" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="E123" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F123" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E123" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="F123" s="7" t="s">
+      <c r="G123" s="6">
+        <v>1</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I123" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G123" s="7">
-        <v>1</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I123" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B124" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C124" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C124" s="7" t="s">
+      <c r="D124" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="E124" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F124" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E124" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F124" s="7" t="s">
+      <c r="G124" s="6">
+        <v>1</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I124" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G124" s="7">
-        <v>1</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I124" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B125" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C125" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="D125" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="E125" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F125" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E125" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="F125" s="7" t="s">
+      <c r="G125" s="6">
+        <v>1</v>
+      </c>
+      <c r="H125" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I125" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G125" s="7">
-        <v>1</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I125" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C126" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="D126" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="E126" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F126" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E126" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F126" s="7" t="s">
+      <c r="G126" s="6">
+        <v>1</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I126" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G126" s="7">
-        <v>1</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I126" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B127" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C127" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="D127" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D127" s="7" t="s">
+      <c r="E127" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F127" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E127" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F127" s="7" t="s">
+      <c r="G127" s="6">
+        <v>2</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I127" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G127" s="7">
-        <v>2</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I127" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B128" s="7" t="s">
+      <c r="B128" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C128" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="D128" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="E128" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F128" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E128" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="F128" s="7" t="s">
+      <c r="G128" s="6">
+        <v>1</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I128" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G128" s="7">
-        <v>1</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I128" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B129" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C129" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="D129" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D129" s="7" t="s">
+      <c r="E129" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F129" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E129" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="F129" s="7" t="s">
+      <c r="G129" s="6">
+        <v>3</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I129" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G129" s="7">
-        <v>3</v>
-      </c>
-      <c r="H129" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I129" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B130" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C130" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="D130" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="E130" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F130" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E130" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="F130" s="7" t="s">
+      <c r="G130" s="6">
+        <v>1</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I130" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G130" s="7">
-        <v>1</v>
-      </c>
-      <c r="H130" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I130" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C131" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="D131" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D131" s="7" t="s">
+      <c r="E131" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F131" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E131" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="F131" s="7" t="s">
+      <c r="G131" s="6">
+        <v>1</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I131" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G131" s="7">
-        <v>1</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I131" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B132" s="7" t="s">
+      <c r="B132" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="D132" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="E132" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F132" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E132" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="F132" s="7" t="s">
+      <c r="G132" s="6">
+        <v>1</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I132" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G132" s="7">
-        <v>1</v>
-      </c>
-      <c r="H132" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I132" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B133" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C133" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="D133" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D133" s="7" t="s">
+      <c r="E133" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F133" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E133" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F133" s="7" t="s">
+      <c r="G133" s="6">
+        <v>1</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I133" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G133" s="7">
-        <v>1</v>
-      </c>
-      <c r="H133" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I133" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B134" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="D134" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="E134" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F134" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E134" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F134" s="7" t="s">
+      <c r="G134" s="6">
+        <v>1</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I134" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G134" s="7">
-        <v>1</v>
-      </c>
-      <c r="H134" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I134" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B135" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C135" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="D135" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D135" s="7" t="s">
+      <c r="E135" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F135" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E135" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F135" s="7" t="s">
+      <c r="G135" s="6">
+        <v>1</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I135" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G135" s="7">
-        <v>1</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I135" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B136" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C136" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="D136" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D136" s="7" t="s">
+      <c r="E136" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F136" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E136" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F136" s="7" t="s">
+      <c r="G136" s="6">
+        <v>1</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I136" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G136" s="7">
-        <v>1</v>
-      </c>
-      <c r="H136" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I136" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="D137" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D137" s="7" t="s">
+      <c r="E137" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F137" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E137" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="F137" s="7" t="s">
+      <c r="G137" s="6">
+        <v>1</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I137" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G137" s="7">
-        <v>1</v>
-      </c>
-      <c r="H137" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I137" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B138" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="D138" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="E138" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F138" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E138" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="F138" s="7" t="s">
+      <c r="G138" s="6">
+        <v>1</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I138" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G138" s="7">
-        <v>1</v>
-      </c>
-      <c r="H138" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I138" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C139" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C139" s="7" t="s">
+      <c r="D139" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D139" s="7" t="s">
+      <c r="E139" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F139" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E139" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F139" s="7" t="s">
+      <c r="G139" s="6">
+        <v>1</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I139" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G139" s="7">
-        <v>1</v>
-      </c>
-      <c r="H139" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I139" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B140" s="7" t="s">
+      <c r="B140" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C140" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="D140" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="E140" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F140" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E140" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="F140" s="7" t="s">
+      <c r="G140" s="6">
+        <v>2</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I140" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G140" s="7">
-        <v>2</v>
-      </c>
-      <c r="H140" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I140" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B141" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="D141" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D141" s="7" t="s">
+      <c r="E141" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F141" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E141" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F141" s="7" t="s">
+      <c r="G141" s="6">
+        <v>1</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I141" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G141" s="7">
-        <v>1</v>
-      </c>
-      <c r="H141" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I141" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="B142" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="D142" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D142" s="7" t="s">
+      <c r="E142" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F142" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E142" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="F142" s="7" t="s">
+      <c r="G142" s="6">
+        <v>1</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I142" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G142" s="7">
-        <v>1</v>
-      </c>
-      <c r="H142" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I142" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B143" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="D143" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D143" s="7" t="s">
+      <c r="E143" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F143" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E143" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="F143" s="7" t="s">
+      <c r="G143" s="6">
+        <v>1</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I143" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G143" s="7">
-        <v>1</v>
-      </c>
-      <c r="H143" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I143" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B144" s="7" t="s">
+      <c r="B144" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C144" s="7" t="s">
+      <c r="D144" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D144" s="7" t="s">
+      <c r="E144" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F144" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E144" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="F144" s="7" t="s">
+      <c r="G144" s="6">
+        <v>1</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I144" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G144" s="7">
-        <v>1</v>
-      </c>
-      <c r="H144" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I144" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B145" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C145" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="D145" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D145" s="7" t="s">
+      <c r="E145" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F145" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E145" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F145" s="7" t="s">
+      <c r="G145" s="6">
+        <v>1</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I145" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G145" s="7">
-        <v>1</v>
-      </c>
-      <c r="H145" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I145" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="D146" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D146" s="7" t="s">
+      <c r="E146" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F146" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E146" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="F146" s="7" t="s">
+      <c r="G146" s="6">
+        <v>1</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I146" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G146" s="7">
-        <v>1</v>
-      </c>
-      <c r="H146" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I146" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C147" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="D147" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D147" s="7" t="s">
+      <c r="E147" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F147" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E147" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="F147" s="7" t="s">
+      <c r="G147" s="6">
+        <v>1</v>
+      </c>
+      <c r="H147" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I147" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G147" s="7">
-        <v>1</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C148" s="7" t="s">
+      <c r="D148" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D148" s="7" t="s">
+      <c r="E148" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F148" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E148" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="F148" s="7" t="s">
+      <c r="G148" s="6">
+        <v>1</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I148" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G148" s="7">
-        <v>1</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I148" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B149" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C149" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="D149" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D149" s="7" t="s">
+      <c r="E149" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F149" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E149" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="F149" s="7" t="s">
+      <c r="G149" s="6">
+        <v>1</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I149" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G149" s="7">
-        <v>1</v>
-      </c>
-      <c r="H149" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I149" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C150" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C150" s="7" t="s">
+      <c r="D150" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D150" s="7" t="s">
+      <c r="E150" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F150" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E150" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="F150" s="7" t="s">
+      <c r="G150" s="6">
+        <v>4</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I150" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G150" s="7">
-        <v>4</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I150" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="B151" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C151" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="D151" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D151" s="7" t="s">
+      <c r="E151" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F151" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="E151" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="F151" s="7" t="s">
+      <c r="G151" s="6">
+        <v>1</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I151" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="G151" s="7">
-        <v>1</v>
-      </c>
-      <c r="H151" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="I151" s="7" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B152" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C152" s="7" t="s">
+      <c r="B152" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C152" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D152" s="7" t="s">
+      <c r="D152" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E152" s="7" t="s">
+      <c r="E152" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F152" s="7" t="s">
+      <c r="F152" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G152" s="7">
+      <c r="G152" s="6">
         <v>32</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="H152" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="I152" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6505,28 +6610,28 @@
       <c r="A153" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B153" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C153" s="7" t="s">
+      <c r="B153" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C153" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D153" s="7" t="s">
+      <c r="D153" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E153" s="7" t="s">
+      <c r="E153" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F153" s="7" t="s">
+      <c r="F153" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G153" s="6">
         <v>32</v>
       </c>
-      <c r="H153" s="7" t="s">
+      <c r="H153" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I153" s="7" t="s">
+      <c r="I153" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6534,28 +6639,28 @@
       <c r="A154" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B154" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C154" s="7" t="s">
+      <c r="B154" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C154" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="D154" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E154" s="7" t="s">
+      <c r="E154" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F154" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G154" s="7">
-        <v>1</v>
-      </c>
-      <c r="H154" s="7" t="s">
+      <c r="G154" s="6">
+        <v>1</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I154" s="7" t="s">
+      <c r="I154" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6563,28 +6668,28 @@
       <c r="A155" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B155" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C155" s="7" t="s">
+      <c r="B155" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C155" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D155" s="7" t="s">
+      <c r="D155" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="E155" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F155" s="7" t="s">
+      <c r="F155" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G155" s="7">
-        <v>1</v>
-      </c>
-      <c r="H155" s="7" t="s">
+      <c r="G155" s="6">
+        <v>1</v>
+      </c>
+      <c r="H155" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I155" s="7" t="s">
+      <c r="I155" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6592,28 +6697,28 @@
       <c r="A156" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B156" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C156" s="7" t="s">
+      <c r="B156" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C156" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D156" s="7" t="s">
+      <c r="D156" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E156" s="7" t="s">
+      <c r="E156" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="F156" s="7" t="s">
+      <c r="F156" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G156" s="7">
-        <v>1</v>
-      </c>
-      <c r="H156" s="7" t="s">
+      <c r="G156" s="6">
+        <v>1</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I156" s="7" t="s">
+      <c r="I156" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6621,28 +6726,28 @@
       <c r="A157" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B157" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C157" s="7" t="s">
+      <c r="B157" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C157" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D157" s="7" t="s">
+      <c r="D157" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E157" s="7" t="s">
+      <c r="E157" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="F157" s="7" t="s">
+      <c r="F157" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G157" s="7">
+      <c r="G157" s="6">
         <v>31</v>
       </c>
-      <c r="H157" s="7" t="s">
+      <c r="H157" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I157" s="7" t="s">
+      <c r="I157" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6650,28 +6755,28 @@
       <c r="A158" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B158" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C158" s="7" t="s">
+      <c r="B158" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C158" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D158" s="7" t="s">
+      <c r="D158" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E158" s="7" t="s">
+      <c r="E158" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F158" s="7" t="s">
+      <c r="F158" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G158" s="7">
-        <v>1</v>
-      </c>
-      <c r="H158" s="7" t="s">
+      <c r="G158" s="6">
+        <v>1</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I158" s="7" t="s">
+      <c r="I158" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6679,28 +6784,28 @@
       <c r="A159" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B159" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C159" s="7" t="s">
+      <c r="B159" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C159" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D159" s="7" t="s">
+      <c r="D159" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E159" s="7" t="s">
+      <c r="E159" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F159" s="7" t="s">
+      <c r="F159" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G159" s="7">
-        <v>1</v>
-      </c>
-      <c r="H159" s="7" t="s">
+      <c r="G159" s="6">
+        <v>1</v>
+      </c>
+      <c r="H159" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I159" s="7" t="s">
+      <c r="I159" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6708,28 +6813,28 @@
       <c r="A160" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B160" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C160" s="7" t="s">
+      <c r="B160" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C160" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="D160" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="E160" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="F160" s="7" t="s">
+      <c r="F160" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G160" s="7">
-        <v>1</v>
-      </c>
-      <c r="H160" s="7" t="s">
+      <c r="G160" s="6">
+        <v>1</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I160" s="7" t="s">
+      <c r="I160" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6737,28 +6842,28 @@
       <c r="A161" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B161" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C161" s="7" t="s">
+      <c r="B161" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C161" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D161" s="7" t="s">
+      <c r="D161" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E161" s="7" t="s">
+      <c r="E161" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F161" s="7" t="s">
+      <c r="F161" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G161" s="7">
-        <v>1</v>
-      </c>
-      <c r="H161" s="7" t="s">
+      <c r="G161" s="6">
+        <v>1</v>
+      </c>
+      <c r="H161" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I161" s="7" t="s">
+      <c r="I161" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6766,28 +6871,28 @@
       <c r="A162" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B162" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C162" s="7" t="s">
+      <c r="B162" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C162" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D162" s="7" t="s">
+      <c r="D162" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E162" s="7" t="s">
+      <c r="E162" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="F162" s="7" t="s">
+      <c r="F162" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G162" s="7">
-        <v>1</v>
-      </c>
-      <c r="H162" s="7" t="s">
+      <c r="G162" s="6">
+        <v>1</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I162" s="7" t="s">
+      <c r="I162" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6795,28 +6900,28 @@
       <c r="A163" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B163" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C163" s="7" t="s">
+      <c r="B163" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C163" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D163" s="7" t="s">
+      <c r="D163" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E163" s="7" t="s">
+      <c r="E163" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F163" s="7" t="s">
+      <c r="F163" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G163" s="7">
-        <v>1</v>
-      </c>
-      <c r="H163" s="7" t="s">
+      <c r="G163" s="6">
+        <v>1</v>
+      </c>
+      <c r="H163" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I163" s="7" t="s">
+      <c r="I163" s="6" t="s">
         <v>233</v>
       </c>
     </row>
@@ -6824,28 +6929,28 @@
       <c r="A164" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B164" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C164" s="7" t="s">
+      <c r="B164" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C164" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D164" s="7" t="s">
+      <c r="D164" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E164" s="7" t="s">
+      <c r="E164" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F164" s="7" t="s">
+      <c r="F164" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G164" s="7">
-        <v>1</v>
-      </c>
-      <c r="H164" s="7" t="s">
+      <c r="G164" s="6">
+        <v>1</v>
+      </c>
+      <c r="H164" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I164" s="7" t="s">
+      <c r="I164" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6853,28 +6958,28 @@
       <c r="A165" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B165" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C165" s="7" t="s">
+      <c r="B165" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C165" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D165" s="7" t="s">
+      <c r="D165" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E165" s="7" t="s">
+      <c r="E165" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F165" s="7" t="s">
+      <c r="F165" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G165" s="7">
+      <c r="G165" s="6">
         <v>2</v>
       </c>
-      <c r="H165" s="7" t="s">
+      <c r="H165" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I165" s="7" t="s">
+      <c r="I165" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6882,28 +6987,28 @@
       <c r="A166" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B166" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C166" s="7" t="s">
+      <c r="B166" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C166" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D166" s="7" t="s">
+      <c r="D166" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E166" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="F166" s="7" t="s">
+      <c r="F166" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G166" s="7">
-        <v>1</v>
-      </c>
-      <c r="H166" s="7" t="s">
+      <c r="G166" s="6">
+        <v>1</v>
+      </c>
+      <c r="H166" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I166" s="7" t="s">
+      <c r="I166" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6911,28 +7016,28 @@
       <c r="A167" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B167" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C167" s="7" t="s">
+      <c r="B167" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C167" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D167" s="7" t="s">
+      <c r="D167" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E167" s="7" t="s">
+      <c r="E167" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="F167" s="7" t="s">
+      <c r="F167" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G167" s="7">
+      <c r="G167" s="6">
         <v>33</v>
       </c>
-      <c r="H167" s="7" t="s">
+      <c r="H167" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I167" s="7" t="s">
+      <c r="I167" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6940,28 +7045,28 @@
       <c r="A168" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B168" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C168" s="7" t="s">
+      <c r="B168" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C168" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D168" s="7" t="s">
+      <c r="D168" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E168" s="7" t="s">
+      <c r="E168" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F168" s="7" t="s">
+      <c r="F168" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G168" s="7">
+      <c r="G168" s="6">
         <v>34</v>
       </c>
-      <c r="H168" s="7" t="s">
+      <c r="H168" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I168" s="7" t="s">
+      <c r="I168" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6969,28 +7074,28 @@
       <c r="A169" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B169" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C169" s="7" t="s">
+      <c r="B169" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C169" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D169" s="7" t="s">
+      <c r="D169" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E169" s="7" t="s">
+      <c r="E169" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F169" s="7" t="s">
+      <c r="F169" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G169" s="7">
+      <c r="G169" s="6">
         <v>29</v>
       </c>
-      <c r="H169" s="7" t="s">
+      <c r="H169" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I169" s="7" t="s">
+      <c r="I169" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -6998,28 +7103,28 @@
       <c r="A170" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B170" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C170" s="7" t="s">
+      <c r="B170" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C170" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D170" s="7" t="s">
+      <c r="D170" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E170" s="7" t="s">
+      <c r="E170" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F170" s="7" t="s">
+      <c r="F170" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G170" s="7">
-        <v>1</v>
-      </c>
-      <c r="H170" s="7" t="s">
+      <c r="G170" s="6">
+        <v>1</v>
+      </c>
+      <c r="H170" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I170" s="7" t="s">
+      <c r="I170" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -7027,28 +7132,28 @@
       <c r="A171" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B171" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C171" s="7" t="s">
+      <c r="B171" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C171" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D171" s="7" t="s">
+      <c r="D171" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E171" s="7" t="s">
+      <c r="E171" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F171" s="7" t="s">
+      <c r="F171" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G171" s="7">
-        <v>1</v>
-      </c>
-      <c r="H171" s="7" t="s">
+      <c r="G171" s="6">
+        <v>1</v>
+      </c>
+      <c r="H171" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I171" s="7" t="s">
+      <c r="I171" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -7056,28 +7161,28 @@
       <c r="A172" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B172" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C172" s="7" t="s">
+      <c r="B172" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C172" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D172" s="7" t="s">
+      <c r="D172" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E172" s="7" t="s">
+      <c r="E172" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="F172" s="7" t="s">
+      <c r="F172" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G172" s="7">
-        <v>1</v>
-      </c>
-      <c r="H172" s="7" t="s">
+      <c r="G172" s="6">
+        <v>1</v>
+      </c>
+      <c r="H172" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I172" s="7" t="s">
+      <c r="I172" s="6" t="s">
         <v>248</v>
       </c>
     </row>
@@ -7085,28 +7190,28 @@
       <c r="A173" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B173" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C173" s="7" t="s">
+      <c r="B173" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C173" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D173" s="7" t="s">
+      <c r="D173" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E173" s="7" t="s">
+      <c r="E173" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F173" s="7" t="s">
+      <c r="F173" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G173" s="7">
+      <c r="G173" s="6">
         <v>36</v>
       </c>
-      <c r="H173" s="7" t="s">
+      <c r="H173" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I173" s="7" t="s">
+      <c r="I173" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -7114,28 +7219,28 @@
       <c r="A174" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B174" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C174" s="7" t="s">
+      <c r="B174" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C174" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D174" s="7" t="s">
+      <c r="D174" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E174" s="7" t="s">
+      <c r="E174" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F174" s="7" t="s">
+      <c r="F174" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G174" s="7">
-        <v>1</v>
-      </c>
-      <c r="H174" s="7" t="s">
+      <c r="G174" s="6">
+        <v>1</v>
+      </c>
+      <c r="H174" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I174" s="7" t="s">
+      <c r="I174" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -7143,28 +7248,28 @@
       <c r="A175" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B175" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C175" s="7" t="s">
+      <c r="B175" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C175" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D175" s="7" t="s">
+      <c r="D175" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E175" s="7" t="s">
+      <c r="E175" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F175" s="7" t="s">
+      <c r="F175" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="G175" s="7">
+      <c r="G175" s="6">
         <v>34</v>
       </c>
-      <c r="H175" s="7" t="s">
+      <c r="H175" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I175" s="7" t="s">
+      <c r="I175" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -7172,28 +7277,28 @@
       <c r="A176" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B176" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C176" s="7" t="s">
+      <c r="B176" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C176" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D176" s="7" t="s">
+      <c r="D176" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E176" s="7" t="s">
+      <c r="E176" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F176" s="7" t="s">
+      <c r="F176" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G176" s="7">
+      <c r="G176" s="6">
         <v>33</v>
       </c>
-      <c r="H176" s="7" t="s">
+      <c r="H176" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I176" s="7" t="s">
+      <c r="I176" s="6" t="s">
         <v>257</v>
       </c>
     </row>
@@ -7201,28 +7306,28 @@
       <c r="A177" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B177" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C177" s="7" t="s">
+      <c r="B177" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C177" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D177" s="7" t="s">
+      <c r="D177" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E177" s="7" t="s">
+      <c r="E177" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F177" s="7" t="s">
+      <c r="F177" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G177" s="7">
+      <c r="G177" s="6">
         <v>35</v>
       </c>
-      <c r="H177" s="7" t="s">
+      <c r="H177" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I177" s="7" t="s">
+      <c r="I177" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7230,28 +7335,28 @@
       <c r="A178" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B178" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C178" s="7" t="s">
+      <c r="B178" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C178" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D178" s="7" t="s">
+      <c r="D178" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E178" s="7" t="s">
+      <c r="E178" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="F178" s="7" t="s">
+      <c r="F178" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G178" s="7">
-        <v>1</v>
-      </c>
-      <c r="H178" s="7" t="s">
+      <c r="G178" s="6">
+        <v>1</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I178" s="7" t="s">
+      <c r="I178" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7259,28 +7364,28 @@
       <c r="A179" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B179" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C179" s="7" t="s">
+      <c r="B179" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C179" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D179" s="7" t="s">
+      <c r="D179" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E179" s="7" t="s">
+      <c r="E179" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F179" s="7" t="s">
+      <c r="F179" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G179" s="7">
-        <v>1</v>
-      </c>
-      <c r="H179" s="7" t="s">
+      <c r="G179" s="6">
+        <v>1</v>
+      </c>
+      <c r="H179" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I179" s="7" t="s">
+      <c r="I179" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7288,28 +7393,28 @@
       <c r="A180" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B180" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C180" s="7" t="s">
+      <c r="B180" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C180" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D180" s="7" t="s">
+      <c r="D180" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E180" s="7" t="s">
+      <c r="E180" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F180" s="7" t="s">
+      <c r="F180" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G180" s="7">
-        <v>1</v>
-      </c>
-      <c r="H180" s="7" t="s">
+      <c r="G180" s="6">
+        <v>1</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I180" s="7" t="s">
+      <c r="I180" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7317,28 +7422,28 @@
       <c r="A181" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B181" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C181" s="7" t="s">
+      <c r="B181" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C181" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D181" s="7" t="s">
+      <c r="D181" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E181" s="7" t="s">
+      <c r="E181" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="F181" s="7" t="s">
+      <c r="F181" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G181" s="7">
+      <c r="G181" s="6">
         <v>35</v>
       </c>
-      <c r="H181" s="7" t="s">
+      <c r="H181" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I181" s="7" t="s">
+      <c r="I181" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7346,28 +7451,28 @@
       <c r="A182" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B182" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C182" s="7" t="s">
+      <c r="B182" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C182" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D182" s="7" t="s">
+      <c r="D182" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E182" s="7" t="s">
+      <c r="E182" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="F182" s="7" t="s">
+      <c r="F182" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G182" s="7">
+      <c r="G182" s="6">
         <v>31</v>
       </c>
-      <c r="H182" s="7" t="s">
+      <c r="H182" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I182" s="7" t="s">
+      <c r="I182" s="6" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7375,28 +7480,28 @@
       <c r="A183" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B183" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C183" s="7" t="s">
+      <c r="B183" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C183" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D183" s="7" t="s">
+      <c r="D183" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E183" s="7" t="s">
+      <c r="E183" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F183" s="7" t="s">
+      <c r="F183" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G183" s="7">
-        <v>1</v>
-      </c>
-      <c r="H183" s="7" t="s">
+      <c r="G183" s="6">
+        <v>1</v>
+      </c>
+      <c r="H183" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I183" s="7" t="s">
+      <c r="I183" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7404,28 +7509,28 @@
       <c r="A184" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B184" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C184" s="7" t="s">
+      <c r="B184" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C184" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D184" s="7" t="s">
+      <c r="D184" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E184" s="7" t="s">
+      <c r="E184" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="F184" s="7" t="s">
+      <c r="F184" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G184" s="7">
+      <c r="G184" s="6">
         <v>26</v>
       </c>
-      <c r="H184" s="7" t="s">
+      <c r="H184" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I184" s="7" t="s">
+      <c r="I184" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7433,28 +7538,28 @@
       <c r="A185" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B185" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C185" s="7" t="s">
+      <c r="B185" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C185" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D185" s="7" t="s">
+      <c r="D185" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E185" s="7" t="s">
+      <c r="E185" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="F185" s="7" t="s">
+      <c r="F185" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G185" s="7">
-        <v>1</v>
-      </c>
-      <c r="H185" s="7" t="s">
+      <c r="G185" s="6">
+        <v>1</v>
+      </c>
+      <c r="H185" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I185" s="7" t="s">
+      <c r="I185" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7462,28 +7567,28 @@
       <c r="A186" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B186" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C186" s="7" t="s">
+      <c r="B186" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C186" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D186" s="7" t="s">
+      <c r="D186" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E186" s="7" t="s">
+      <c r="E186" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="F186" s="7" t="s">
+      <c r="F186" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G186" s="7">
+      <c r="G186" s="6">
         <v>2</v>
       </c>
-      <c r="H186" s="7" t="s">
+      <c r="H186" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I186" s="7" t="s">
+      <c r="I186" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7491,28 +7596,28 @@
       <c r="A187" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B187" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C187" s="7" t="s">
+      <c r="B187" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C187" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D187" s="7" t="s">
+      <c r="D187" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E187" s="7" t="s">
+      <c r="E187" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F187" s="7" t="s">
+      <c r="F187" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G187" s="7">
-        <v>1</v>
-      </c>
-      <c r="H187" s="7" t="s">
+      <c r="G187" s="6">
+        <v>1</v>
+      </c>
+      <c r="H187" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I187" s="7" t="s">
+      <c r="I187" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7520,28 +7625,28 @@
       <c r="A188" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B188" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C188" s="7" t="s">
+      <c r="B188" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C188" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D188" s="7" t="s">
+      <c r="D188" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E188" s="7" t="s">
+      <c r="E188" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F188" s="7" t="s">
+      <c r="F188" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G188" s="7">
+      <c r="G188" s="6">
         <v>34</v>
       </c>
-      <c r="H188" s="7" t="s">
+      <c r="H188" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I188" s="7" t="s">
+      <c r="I188" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7549,28 +7654,28 @@
       <c r="A189" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B189" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C189" s="7" t="s">
+      <c r="B189" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C189" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D189" s="7" t="s">
+      <c r="D189" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E189" s="7" t="s">
+      <c r="E189" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F189" s="7" t="s">
+      <c r="F189" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G189" s="7">
+      <c r="G189" s="6">
         <v>2</v>
       </c>
-      <c r="H189" s="7" t="s">
+      <c r="H189" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I189" s="7" t="s">
+      <c r="I189" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7578,28 +7683,28 @@
       <c r="A190" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B190" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C190" s="7" t="s">
+      <c r="B190" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C190" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D190" s="7" t="s">
+      <c r="D190" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E190" s="7" t="s">
+      <c r="E190" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="F190" s="7" t="s">
+      <c r="F190" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G190" s="7">
+      <c r="G190" s="6">
         <v>36</v>
       </c>
-      <c r="H190" s="7" t="s">
+      <c r="H190" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I190" s="7" t="s">
+      <c r="I190" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7607,28 +7712,28 @@
       <c r="A191" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B191" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C191" s="7" t="s">
+      <c r="B191" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C191" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D191" s="7" t="s">
+      <c r="D191" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E191" s="7" t="s">
+      <c r="E191" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="F191" s="7" t="s">
+      <c r="F191" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G191" s="7">
-        <v>1</v>
-      </c>
-      <c r="H191" s="7" t="s">
+      <c r="G191" s="6">
+        <v>1</v>
+      </c>
+      <c r="H191" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I191" s="7" t="s">
+      <c r="I191" s="6" t="s">
         <v>266</v>
       </c>
     </row>
@@ -7636,28 +7741,28 @@
       <c r="A192" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B192" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C192" s="7" t="s">
+      <c r="B192" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C192" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D192" s="7" t="s">
+      <c r="D192" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E192" s="7" t="s">
+      <c r="E192" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="F192" s="7" t="s">
+      <c r="F192" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G192" s="7">
-        <v>1</v>
-      </c>
-      <c r="H192" s="7" t="s">
+      <c r="G192" s="6">
+        <v>1</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I192" s="7" t="s">
+      <c r="I192" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7665,28 +7770,28 @@
       <c r="A193" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B193" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C193" s="7" t="s">
+      <c r="B193" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C193" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D193" s="7" t="s">
+      <c r="D193" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E193" s="7" t="s">
+      <c r="E193" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F193" s="7" t="s">
+      <c r="F193" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G193" s="7">
+      <c r="G193" s="6">
         <v>13</v>
       </c>
-      <c r="H193" s="7" t="s">
+      <c r="H193" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I193" s="7" t="s">
+      <c r="I193" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7694,28 +7799,28 @@
       <c r="A194" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B194" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C194" s="7" t="s">
+      <c r="B194" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C194" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D194" s="7" t="s">
+      <c r="D194" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E194" s="7" t="s">
+      <c r="E194" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="F194" s="7" t="s">
+      <c r="F194" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="G194" s="7">
+      <c r="G194" s="6">
         <v>12</v>
       </c>
-      <c r="H194" s="7" t="s">
+      <c r="H194" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I194" s="7" t="s">
+      <c r="I194" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7723,28 +7828,28 @@
       <c r="A195" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B195" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C195" s="7" t="s">
+      <c r="B195" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C195" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D195" s="7" t="s">
+      <c r="D195" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E195" s="7" t="s">
+      <c r="E195" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="F195" s="7" t="s">
+      <c r="F195" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G195" s="7">
+      <c r="G195" s="6">
         <v>36</v>
       </c>
-      <c r="H195" s="7" t="s">
+      <c r="H195" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I195" s="7" t="s">
+      <c r="I195" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7752,28 +7857,28 @@
       <c r="A196" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B196" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C196" s="7" t="s">
+      <c r="B196" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C196" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D196" s="7" t="s">
+      <c r="D196" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E196" s="7" t="s">
+      <c r="E196" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="F196" s="7" t="s">
+      <c r="F196" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G196" s="7">
-        <v>1</v>
-      </c>
-      <c r="H196" s="7" t="s">
+      <c r="G196" s="6">
+        <v>1</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I196" s="7" t="s">
+      <c r="I196" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7781,28 +7886,28 @@
       <c r="A197" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B197" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C197" s="7" t="s">
+      <c r="B197" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C197" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D197" s="7" t="s">
+      <c r="D197" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E197" s="7" t="s">
+      <c r="E197" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="F197" s="7" t="s">
+      <c r="F197" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G197" s="7">
+      <c r="G197" s="6">
         <v>36</v>
       </c>
-      <c r="H197" s="7" t="s">
+      <c r="H197" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I197" s="7" t="s">
+      <c r="I197" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7810,28 +7915,28 @@
       <c r="A198" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B198" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="C198" s="7" t="s">
+      <c r="B198" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C198" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="D198" s="7" t="s">
+      <c r="D198" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E198" s="7" t="s">
+      <c r="E198" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F198" s="7" t="s">
+      <c r="F198" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="G198" s="7">
-        <v>1</v>
-      </c>
-      <c r="H198" s="7" t="s">
+      <c r="G198" s="6">
+        <v>1</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I198" s="7" t="s">
+      <c r="I198" s="6" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7839,28 +7944,28 @@
       <c r="A199" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C199" s="7" t="s">
+      <c r="C199" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D199" s="7" t="s">
+      <c r="D199" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E199" s="7" t="s">
+      <c r="E199" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F199" s="7" t="s">
+      <c r="F199" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="G199" s="7">
+      <c r="G199" s="6">
         <v>28</v>
       </c>
-      <c r="H199" s="7" t="s">
+      <c r="H199" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I199" s="7" t="s">
+      <c r="I199" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -7868,28 +7973,28 @@
       <c r="A200" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C200" s="7" t="s">
+      <c r="C200" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D200" s="7" t="s">
+      <c r="D200" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E200" s="7" t="s">
+      <c r="E200" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F200" s="7" t="s">
+      <c r="F200" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="G200" s="7">
+      <c r="G200" s="6">
         <v>30</v>
       </c>
-      <c r="H200" s="7" t="s">
+      <c r="H200" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I200" s="7" t="s">
+      <c r="I200" s="6" t="s">
         <v>78</v>
       </c>
     </row>
@@ -7897,28 +8002,28 @@
       <c r="A201" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C201" s="7" t="s">
+      <c r="C201" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D201" s="7" t="s">
+      <c r="D201" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E201" s="7" t="s">
+      <c r="E201" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="F201" s="7" t="s">
+      <c r="F201" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G201" s="7">
-        <v>1</v>
-      </c>
-      <c r="H201" s="7" t="s">
+      <c r="G201" s="6">
+        <v>1</v>
+      </c>
+      <c r="H201" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I201" s="7" t="s">
+      <c r="I201" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7926,28 +8031,28 @@
       <c r="A202" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C202" s="7" t="s">
+      <c r="C202" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D202" s="7" t="s">
+      <c r="D202" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E202" s="7" t="s">
+      <c r="E202" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F202" s="7" t="s">
+      <c r="F202" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="G202" s="7">
+      <c r="G202" s="6">
         <v>35</v>
       </c>
-      <c r="H202" s="7" t="s">
+      <c r="H202" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I202" s="7" t="s">
+      <c r="I202" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7955,28 +8060,28 @@
       <c r="A203" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C203" s="7" t="s">
+      <c r="C203" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D203" s="7" t="s">
+      <c r="D203" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E203" s="7" t="s">
+      <c r="E203" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F203" s="7" t="s">
+      <c r="F203" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G203" s="7">
+      <c r="G203" s="6">
         <v>32</v>
       </c>
-      <c r="H203" s="7" t="s">
+      <c r="H203" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I203" s="7" t="s">
+      <c r="I203" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7984,28 +8089,28 @@
       <c r="A204" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B204" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C204" s="7" t="s">
+      <c r="C204" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D204" s="7" t="s">
+      <c r="D204" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E204" s="7" t="s">
+      <c r="E204" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F204" s="7" t="s">
+      <c r="F204" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="G204" s="7">
+      <c r="G204" s="6">
         <v>32</v>
       </c>
-      <c r="H204" s="7" t="s">
+      <c r="H204" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I204" s="7" t="s">
+      <c r="I204" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -8013,28 +8118,28 @@
       <c r="A205" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B205" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C205" s="7" t="s">
+      <c r="C205" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D205" s="7" t="s">
+      <c r="D205" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E205" s="7" t="s">
+      <c r="E205" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F205" s="7" t="s">
+      <c r="F205" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G205" s="7">
-        <v>1</v>
-      </c>
-      <c r="H205" s="7" t="s">
+      <c r="G205" s="6">
+        <v>1</v>
+      </c>
+      <c r="H205" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I205" s="7" t="s">
+      <c r="I205" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8042,28 +8147,28 @@
       <c r="A206" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="B206" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C206" s="7" t="s">
+      <c r="C206" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D206" s="7" t="s">
+      <c r="D206" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E206" s="7" t="s">
+      <c r="E206" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F206" s="7" t="s">
+      <c r="F206" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="G206" s="7">
+      <c r="G206" s="6">
         <v>33</v>
       </c>
-      <c r="H206" s="7" t="s">
+      <c r="H206" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I206" s="7" t="s">
+      <c r="I206" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8071,28 +8176,28 @@
       <c r="A207" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C207" s="7" t="s">
+      <c r="C207" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D207" s="7" t="s">
+      <c r="D207" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E207" s="7" t="s">
+      <c r="E207" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F207" s="7" t="s">
+      <c r="F207" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G207" s="7">
-        <v>1</v>
-      </c>
-      <c r="H207" s="7" t="s">
+      <c r="G207" s="6">
+        <v>1</v>
+      </c>
+      <c r="H207" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I207" s="7" t="s">
+      <c r="I207" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8100,28 +8205,28 @@
       <c r="A208" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="B208" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C208" s="7" t="s">
+      <c r="C208" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D208" s="7" t="s">
+      <c r="D208" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E208" s="7" t="s">
+      <c r="E208" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F208" s="7" t="s">
+      <c r="F208" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G208" s="7">
+      <c r="G208" s="6">
         <v>32</v>
       </c>
-      <c r="H208" s="7" t="s">
+      <c r="H208" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I208" s="7" t="s">
+      <c r="I208" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8129,28 +8234,28 @@
       <c r="A209" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B209" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C209" s="7" t="s">
+      <c r="C209" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D209" s="7" t="s">
+      <c r="D209" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E209" s="7" t="s">
+      <c r="E209" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F209" s="7" t="s">
+      <c r="F209" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G209" s="7">
+      <c r="G209" s="6">
         <v>32</v>
       </c>
-      <c r="H209" s="7" t="s">
+      <c r="H209" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I209" s="7" t="s">
+      <c r="I209" s="6" t="s">
         <v>31</v>
       </c>
     </row>
@@ -8158,28 +8263,28 @@
       <c r="A210" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C210" s="7" t="s">
+      <c r="C210" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D210" s="7" t="s">
+      <c r="D210" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E210" s="7" t="s">
+      <c r="E210" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F210" s="7" t="s">
+      <c r="F210" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="G210" s="7">
+      <c r="G210" s="6">
         <v>22</v>
       </c>
-      <c r="H210" s="7" t="s">
+      <c r="H210" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I210" s="7" t="s">
+      <c r="I210" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8187,28 +8292,28 @@
       <c r="A211" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B211" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C211" s="7" t="s">
+      <c r="C211" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D211" s="7" t="s">
+      <c r="D211" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E211" s="7" t="s">
+      <c r="E211" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F211" s="7" t="s">
+      <c r="F211" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="G211" s="7">
+      <c r="G211" s="6">
         <v>26</v>
       </c>
-      <c r="H211" s="7" t="s">
+      <c r="H211" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I211" s="7" t="s">
+      <c r="I211" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8216,28 +8321,28 @@
       <c r="A212" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C212" s="7" t="s">
+      <c r="C212" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D212" s="7" t="s">
+      <c r="D212" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E212" s="7" t="s">
+      <c r="E212" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F212" s="7" t="s">
+      <c r="F212" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="G212" s="7">
+      <c r="G212" s="6">
         <v>21</v>
       </c>
-      <c r="H212" s="7" t="s">
+      <c r="H212" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I212" s="7" t="s">
+      <c r="I212" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8245,32 +8350,876 @@
       <c r="A213" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C213" s="7" t="s">
+      <c r="C213" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="D213" s="7" t="s">
+      <c r="D213" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E213" s="7" t="s">
+      <c r="E213" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F213" s="7" t="s">
+      <c r="F213" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G213" s="7">
+      <c r="G213" s="6">
         <v>31</v>
       </c>
-      <c r="H213" s="7" t="s">
+      <c r="H213" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I213" s="7" t="s">
+      <c r="I213" s="6" t="s">
         <v>16</v>
       </c>
     </row>
+    <row r="214" spans="1:9">
+      <c r="A214" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D214" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F214" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G214" s="6">
+        <v>30</v>
+      </c>
+      <c r="H214" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I214" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F215" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G215" s="6">
+        <v>1</v>
+      </c>
+      <c r="H215" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I215" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D216" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F216" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G216" s="6">
+        <v>35</v>
+      </c>
+      <c r="H216" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I216" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D217" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F217" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G217" s="6">
+        <v>1</v>
+      </c>
+      <c r="H217" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I217" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D218" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="F218" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="G218" s="6">
+        <v>32</v>
+      </c>
+      <c r="H218" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I218" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D219" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F219" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G219" s="6">
+        <v>1</v>
+      </c>
+      <c r="H219" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I219" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D220" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="F220" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G220" s="6">
+        <v>1</v>
+      </c>
+      <c r="H220" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I220" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D221" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F221" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G221" s="6">
+        <v>1</v>
+      </c>
+      <c r="H221" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I221" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G222" s="6">
+        <v>30</v>
+      </c>
+      <c r="H222" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I222" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G223" s="6">
+        <v>29</v>
+      </c>
+      <c r="H223" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I223" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D224" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="F224" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G224" s="6">
+        <v>31</v>
+      </c>
+      <c r="H224" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I224" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D225" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F225" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G225" s="6">
+        <v>2</v>
+      </c>
+      <c r="H225" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I225" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D226" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G226" s="6">
+        <v>33</v>
+      </c>
+      <c r="H226" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I226" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D227" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G227" s="6">
+        <v>33</v>
+      </c>
+      <c r="H227" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I227" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D228" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F228" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G228" s="6">
+        <v>31</v>
+      </c>
+      <c r="H228" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="I228" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G229" s="7">
+        <v>1</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E230" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G230" s="7">
+        <v>1</v>
+      </c>
+      <c r="H230" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I230" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E231" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G231" s="7">
+        <v>1</v>
+      </c>
+      <c r="H231" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I231" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E232" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G232" s="7">
+        <v>2</v>
+      </c>
+      <c r="H232" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I232" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E233" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G233" s="7">
+        <v>1</v>
+      </c>
+      <c r="H233" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I233" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E234" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G234" s="7">
+        <v>1</v>
+      </c>
+      <c r="H234" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I234" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E235" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G235" s="7">
+        <v>4</v>
+      </c>
+      <c r="H235" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I235" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E236" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G236" s="7">
+        <v>1</v>
+      </c>
+      <c r="H236" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I236" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E237" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F237" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G237" s="7">
+        <v>3</v>
+      </c>
+      <c r="H237" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I237" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E238" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F238" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G238" s="7">
+        <v>1</v>
+      </c>
+      <c r="H238" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I238" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E239" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G239" s="7">
+        <v>1</v>
+      </c>
+      <c r="H239" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I239" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D240" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E240" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G240" s="7">
+        <v>2</v>
+      </c>
+      <c r="H240" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I240" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D241" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E241" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G241" s="7">
+        <v>2</v>
+      </c>
+      <c r="H241" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I241" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C242" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D242" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E242" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F242" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="G242" s="7">
+        <v>1</v>
+      </c>
+      <c r="H242" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="I242" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I228" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
